--- a/research/traditional_assets/database/data/luxembourg/luxembourg_software_system_application.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_software_system_application.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="F2">
-        <v>-0.741</v>
+        <v>0.266</v>
       </c>
       <c r="G2">
-        <v>0.4334975369458129</v>
+        <v>0.1216939546599496</v>
       </c>
       <c r="H2">
-        <v>0.2563471011746875</v>
+        <v>-0.05761964735516373</v>
       </c>
       <c r="I2">
-        <v>-0.3493747631678666</v>
+        <v>-0.001424748110831234</v>
       </c>
       <c r="J2">
-        <v>-0.3493747631678666</v>
+        <v>-0.001424748110831234</v>
       </c>
       <c r="K2">
-        <v>-199.1</v>
+        <v>-77</v>
       </c>
       <c r="L2">
-        <v>-0.3772262220538083</v>
+        <v>-0.1212216624685138</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.018</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>5.90783773139031e-06</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.0002337662337662337</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,61 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.018</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>135</v>
+        <v>140.5</v>
       </c>
       <c r="V2">
-        <v>0.01747527572101693</v>
+        <v>0.04611395562557437</v>
+      </c>
+      <c r="W2">
+        <v>-0.03575242605748247</v>
       </c>
       <c r="X2">
-        <v>0.06667196389938539</v>
+        <v>0.1308440105360046</v>
+      </c>
+      <c r="Y2">
+        <v>-0.1665964365934871</v>
+      </c>
+      <c r="Z2">
+        <v>3.132149901380675</v>
+      </c>
+      <c r="AA2">
+        <v>-0.004462524654832353</v>
       </c>
       <c r="AB2">
-        <v>0.06360747847116828</v>
+        <v>0.1167726478750659</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1212351725298983</v>
       </c>
       <c r="AD2">
-        <v>757.4</v>
+        <v>728.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>757.4</v>
+        <v>728.8</v>
       </c>
       <c r="AG2">
-        <v>622.4</v>
+        <v>588.3</v>
       </c>
       <c r="AH2">
-        <v>0.08928866149529625</v>
+        <v>0.1930289225553554</v>
       </c>
       <c r="AI2">
-        <v>0.2601765655594105</v>
+        <v>0.2457181389076197</v>
       </c>
       <c r="AJ2">
-        <v>0.07456035267621831</v>
+        <v>0.1618387389617892</v>
       </c>
       <c r="AK2">
-        <v>0.2241994164475343</v>
+        <v>0.2082109361175013</v>
       </c>
       <c r="AL2">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="AM2">
-        <v>52</v>
+        <v>52.832</v>
       </c>
       <c r="AN2">
-        <v>-16.79379157427938</v>
+        <v>5.512859304084721</v>
       </c>
       <c r="AO2">
-        <v>-3.546153846153846</v>
+        <v>-0.01704331450094162</v>
       </c>
       <c r="AP2">
-        <v>-13.80044345898004</v>
+        <v>4.450075642965205</v>
       </c>
       <c r="AQ2">
-        <v>-3.546153846153846</v>
+        <v>-0.01712976983646275</v>
       </c>
     </row>
     <row r="3">
@@ -701,34 +719,34 @@
         </is>
       </c>
       <c r="F3">
-        <v>-0.741</v>
+        <v>0.266</v>
       </c>
       <c r="G3">
-        <v>0.4334975369458129</v>
+        <v>0.1216939546599496</v>
       </c>
       <c r="H3">
-        <v>0.2563471011746875</v>
+        <v>-0.05761964735516373</v>
       </c>
       <c r="I3">
-        <v>-0.3493747631678666</v>
+        <v>-0.001424748110831234</v>
       </c>
       <c r="J3">
-        <v>-0.3493747631678666</v>
+        <v>-0.001424748110831234</v>
       </c>
       <c r="K3">
-        <v>-199.1</v>
+        <v>-77</v>
       </c>
       <c r="L3">
-        <v>-0.3772262220538083</v>
+        <v>-0.1212216624685138</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.018</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>5.90783773139031e-06</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.0002337662337662337</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -740,61 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.018</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>135</v>
+        <v>140.5</v>
       </c>
       <c r="V3">
-        <v>0.01747527572101693</v>
+        <v>0.04611395562557437</v>
+      </c>
+      <c r="W3">
+        <v>-0.03575242605748247</v>
       </c>
       <c r="X3">
-        <v>0.06667196389938539</v>
+        <v>0.1308440105360046</v>
+      </c>
+      <c r="Y3">
+        <v>-0.1665964365934871</v>
+      </c>
+      <c r="Z3">
+        <v>3.132149901380675</v>
+      </c>
+      <c r="AA3">
+        <v>-0.004462524654832353</v>
       </c>
       <c r="AB3">
-        <v>0.06360747847116828</v>
+        <v>0.1167726478750659</v>
+      </c>
+      <c r="AC3">
+        <v>-0.1212351725298983</v>
       </c>
       <c r="AD3">
-        <v>757.4</v>
+        <v>728.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>757.4</v>
+        <v>728.8</v>
       </c>
       <c r="AG3">
-        <v>622.4</v>
+        <v>588.3</v>
       </c>
       <c r="AH3">
-        <v>0.08928866149529625</v>
+        <v>0.1930289225553554</v>
       </c>
       <c r="AI3">
-        <v>0.2601765655594105</v>
+        <v>0.2457181389076197</v>
       </c>
       <c r="AJ3">
-        <v>0.07456035267621831</v>
+        <v>0.1618387389617892</v>
       </c>
       <c r="AK3">
-        <v>0.2241994164475343</v>
+        <v>0.2082109361175013</v>
       </c>
       <c r="AL3">
-        <v>52</v>
+        <v>53.1</v>
       </c>
       <c r="AM3">
-        <v>52</v>
+        <v>52.832</v>
       </c>
       <c r="AN3">
-        <v>-16.79379157427938</v>
+        <v>5.512859304084721</v>
       </c>
       <c r="AO3">
-        <v>-3.546153846153846</v>
+        <v>-0.01704331450094162</v>
       </c>
       <c r="AP3">
-        <v>-13.80044345898004</v>
+        <v>4.450075642965205</v>
       </c>
       <c r="AQ3">
-        <v>-3.546153846153846</v>
+        <v>-0.01712976983646275</v>
       </c>
     </row>
   </sheetData>
